--- a/public/crawlability-blender-september-2026.xlsx
+++ b/public/crawlability-blender-september-2026.xlsx
@@ -39,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +53,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
+        <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -90,13 +85,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -464,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -495,42 +487,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>בינונית</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>לתקן את שורת ה-Sitemap בקובץ robots.txt: היא מצביעה על https://loans.blender.co.il/sitemap.xml.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>daily.blender.co.il: עותק של www.blender.co.il עם canonical לדומיין הראשי אך ללא noindex. להגדיר X-Robots-Tag: noindex.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>לאשר שהעמוד המוגדר noindex אכן אמור להישאר מחוץ לאינדקס.</t>
+          <t>להסיר את שורת ה-Sitemap בקובץ robots.txt (מצביעה על https://loans.blender.co.il/sitemap.xml, דומיין אחר).</t>
         </is>
       </c>
     </row>
@@ -605,7 +567,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/sitemap.xml</t>
         </is>
@@ -659,7 +621,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/sitemap.xml</t>
         </is>
@@ -681,7 +643,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/post-sitemap.xml</t>
         </is>
@@ -703,7 +665,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/page-sitemap.xml</t>
         </is>
@@ -725,7 +687,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/attachment-sitemap.xml</t>
         </is>
@@ -747,7 +709,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/helpie_faq-sitemap.xml</t>
         </is>
@@ -769,7 +731,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/managments-sitemap.xml</t>
         </is>
@@ -791,7 +753,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/partner-sitemap.xml</t>
         </is>
@@ -813,7 +775,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/medias-sitemap.xml</t>
         </is>
@@ -835,7 +797,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/category-sitemap.xml</t>
         </is>
@@ -857,7 +819,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/helpie_faq_category-sitemap.xml</t>
         </is>
@@ -879,7 +841,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>https://loans.blender.co.il/author-sitemap.xml</t>
         </is>
@@ -918,7 +880,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il/</t>
         </is>
@@ -928,7 +890,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il/ (0 הפניות)</t>
         </is>
@@ -940,7 +902,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>http://www.blender.co.il/</t>
         </is>
@@ -950,7 +912,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il:443/ (1 הפניות)</t>
         </is>
@@ -962,7 +924,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>https://blender.co.il/</t>
         </is>
@@ -972,7 +934,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il/ (1 הפניות)</t>
         </is>
@@ -984,7 +946,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>http://blender.co.il/</t>
         </is>
@@ -994,7 +956,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il/ (2 הפניות)</t>
         </is>
@@ -1047,7 +1009,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il</t>
         </is>
@@ -1065,7 +1027,7 @@
           <t>BLender - Partner login</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il/partnerLogin</t>
         </is>
@@ -1087,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1169,7 +1131,7 @@
           <t>noindex</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>https://www.blender.co.il</t>
         </is>
@@ -1185,7 +1147,7 @@
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
@@ -1194,7 +1156,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>daily.blender.co.il</t>
+          <t>loans.blender.co.il</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1204,78 +1166,35 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>בלנדר - הלוואות והשקעות בין אנשים</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.blender.co.il</t>
+          <t>בלנדר | קח הלוואה</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>https://loans.blender.co.il/</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>עותק של האפליקציה ללא noindex</t>
+          <t>אתר שיווקי נפרד (20 כתובות באינדקס)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>עותק של www.blender.co.il עם canonical לדומיין הראשי אך ללא noindex. להגדיר X-Robots-Tag: noindex.</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>loans.blender.co.il</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>בלנדר | קח הלוואה</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>https://loans.blender.co.il/</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>אתר שיווקי נפרד (20 כתובות באינדקס)</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
           <t>ללא פעולה. מפת האתר שב-robots.txt של www.blender.co.il וב-blenderpay.com מצביעה על תת-דומיין זה.</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
